--- a/data/processed/piores_rankings/top 5 piores Frequencia (Posts-Dia).xlsx
+++ b/data/processed/piores_rankings/top 5 piores Frequencia (Posts-Dia).xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,6 +455,174 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Instagram</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fabio Michey Costa Da Silva</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PP - AL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>dep.delegadofabiocosta@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>(61) 3215-5741</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Gabinete 741 - Anexo IV - Câmara dos Deputados</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>15/10/1980</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Recife - PE</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/delegadofabiocosta</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Erika Santos Silva</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PSOL - SP</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>dep.erikahilton@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>(61) 3215-5636</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Gabinete 636 - Anexo IV - Câmara dos Deputados</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>09/12/1992</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Franco da Rocha - SP</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hilton_erika</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Heitor Jose Schuch</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PSB - RS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>dep.heitorschuch@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>(61) 3215-5680</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Gabinete 680 - Anexo III - Câmara dos Deputados</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>25/03/1962</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Santa Cruz do Sul - RS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/heitorschuch</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Paulo Alexandre Pereira Barbosa</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PSDB - SP</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>dep.pauloalexandrebarbosa@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>(61) 3215-5937</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Gabinete 937 - Anexo IV - Câmara dos Deputados</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>09/01/1979</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Santos - SP</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pauloalexandrebarbosa</t>
         </is>
       </c>
     </row>
